--- a/agriculture 44.xlsx
+++ b/agriculture 44.xlsx
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="90">
-  <si>
-    <t xml:space="preserve">Annual Growth rate of State-wise Yield Statistics of Coffee in India(1950-2020)</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="89">
   <si>
     <t xml:space="preserve">Year</t>
   </si>
@@ -320,7 +317,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -342,14 +339,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -423,7 +412,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -432,15 +421,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -460,11 +441,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -489,848 +470,830 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E87"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:E1048576"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="11.44"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="72" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="2"/>
-    </row>
-    <row r="2" customFormat="false" ht="72" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
+      <c r="B15" s="5" t="n">
+        <v>223.493180818302</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1.67419069440348</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1.66334307223794</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>35.8377975181393</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="7" t="n">
-        <v>223.493180818302</v>
-      </c>
-      <c r="C16" s="7" t="n">
-        <v>1.67419069440348</v>
-      </c>
-      <c r="D16" s="7" t="n">
-        <v>1.66334307223794</v>
-      </c>
-      <c r="E16" s="8" t="n">
-        <v>35.8377975181393</v>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>-7.26923849260358</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.475937048582072</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>42.656749201278</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="7" t="n">
-        <v>-7.26923849260358</v>
-      </c>
-      <c r="D17" s="7" t="n">
-        <v>-0.475937048582072</v>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>42.656749201278</v>
+      <c r="B17" s="5" t="n">
+        <v>-100</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-100</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-100</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>-100</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="7" t="n">
-        <v>-100</v>
-      </c>
-      <c r="C18" s="7" t="n">
-        <v>-100</v>
-      </c>
-      <c r="D18" s="7" t="n">
-        <v>-100</v>
-      </c>
-      <c r="E18" s="8" t="n">
-        <v>-100</v>
-      </c>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="6"/>
     </row>
     <row r="19" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="8"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="6"/>
     </row>
     <row r="20" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="8"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="6"/>
     </row>
     <row r="21" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="8"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="6"/>
     </row>
     <row r="22" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="8"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="6"/>
     </row>
     <row r="23" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="8"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="6"/>
     </row>
     <row r="24" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="8"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="6"/>
     </row>
     <row r="25" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="8"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="6"/>
     </row>
     <row r="26" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="8"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="6"/>
     </row>
     <row r="27" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="8"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="6"/>
     </row>
     <row r="28" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="8"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="6"/>
     </row>
     <row r="29" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="8"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="6"/>
     </row>
     <row r="30" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="8"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5" t="n">
+        <v>-11.8503118503119</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>-37.726723095526</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>11.4832535885167</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7" t="n">
-        <v>-11.8503118503119</v>
-      </c>
-      <c r="D31" s="7" t="n">
-        <v>-37.726723095526</v>
-      </c>
-      <c r="E31" s="8" t="n">
-        <v>11.4832535885167</v>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5" t="n">
+        <v>26.1792452830189</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>44.4660194174757</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>-2.14592274678112</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7" t="n">
-        <v>26.1792452830189</v>
-      </c>
-      <c r="D32" s="7" t="n">
-        <v>44.4660194174757</v>
-      </c>
-      <c r="E32" s="8" t="n">
-        <v>-2.14592274678112</v>
+      <c r="B32" s="5"/>
+      <c r="C32" s="5" t="n">
+        <v>-26.5420560747664</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>-48.7903225806452</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>15.3508771929825</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7" t="n">
-        <v>-26.5420560747664</v>
-      </c>
-      <c r="D33" s="7" t="n">
-        <v>-48.7903225806452</v>
-      </c>
-      <c r="E33" s="8" t="n">
-        <v>15.3508771929825</v>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5" t="n">
+        <v>19.5928753180662</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>55.6430446194226</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>-0.190114068441065</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="7"/>
-      <c r="C34" s="7" t="n">
-        <v>19.5928753180662</v>
-      </c>
-      <c r="D34" s="7" t="n">
-        <v>55.6430446194226</v>
-      </c>
-      <c r="E34" s="8" t="n">
-        <v>-0.190114068441065</v>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5" t="n">
+        <v>-3.51063829787234</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>-56.6610455311973</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>-7.04761904761905</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7" t="n">
-        <v>-3.51063829787234</v>
-      </c>
-      <c r="D35" s="7" t="n">
-        <v>-56.6610455311973</v>
-      </c>
-      <c r="E35" s="8" t="n">
-        <v>-7.04761904761905</v>
+      <c r="B35" s="5"/>
+      <c r="C35" s="5" t="n">
+        <v>-22.7122381477398</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>-39.2996108949416</v>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>11.8852459016393</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="5" t="s">
+      <c r="A36" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B36" s="7"/>
-      <c r="C36" s="7" t="n">
-        <v>-22.7122381477398</v>
-      </c>
-      <c r="D36" s="7" t="n">
-        <v>-39.2996108949416</v>
-      </c>
-      <c r="E36" s="8" t="n">
-        <v>11.8852459016393</v>
+      <c r="B36" s="5"/>
+      <c r="C36" s="5" t="n">
+        <v>74.7503566333809</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>287.820512820513</v>
+      </c>
+      <c r="E36" s="6" t="n">
+        <v>4.57875457875458</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="7"/>
-      <c r="C37" s="7" t="n">
-        <v>74.7503566333809</v>
-      </c>
-      <c r="D37" s="7" t="n">
-        <v>287.820512820513</v>
-      </c>
-      <c r="E37" s="8" t="n">
-        <v>4.57875457875458</v>
+      <c r="B37" s="5"/>
+      <c r="C37" s="5" t="n">
+        <v>-41.5510204081633</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>-36.8595041322314</v>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>-20.4903677758319</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B38" s="7"/>
-      <c r="C38" s="7" t="n">
-        <v>-41.5510204081633</v>
-      </c>
-      <c r="D38" s="7" t="n">
-        <v>-36.8595041322314</v>
-      </c>
-      <c r="E38" s="8" t="n">
-        <v>-20.4903677758319</v>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5" t="n">
+        <v>73.6033519553073</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>37.17277486911</v>
+      </c>
+      <c r="E38" s="6" t="n">
+        <v>1.98237885462555</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B39" s="7"/>
-      <c r="C39" s="7" t="n">
-        <v>73.6033519553073</v>
-      </c>
-      <c r="D39" s="7" t="n">
-        <v>37.17277486911</v>
-      </c>
-      <c r="E39" s="8" t="n">
-        <v>1.98237885462555</v>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5" t="n">
+        <v>-37.4094931617056</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>-54.9618320610687</v>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>12.7429805615551</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B40" s="7"/>
-      <c r="C40" s="7" t="n">
-        <v>-37.4094931617056</v>
-      </c>
-      <c r="D40" s="7" t="n">
-        <v>-54.9618320610687</v>
-      </c>
-      <c r="E40" s="8" t="n">
-        <v>12.7429805615551</v>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5" t="n">
+        <v>82.6478149100257</v>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>138.983050847458</v>
+      </c>
+      <c r="E40" s="6" t="n">
+        <v>-15.7088122605364</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="5" t="s">
+      <c r="A41" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7" t="n">
-        <v>82.6478149100257</v>
-      </c>
-      <c r="D41" s="7" t="n">
-        <v>138.983050847458</v>
-      </c>
-      <c r="E41" s="8" t="n">
-        <v>-15.7088122605364</v>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5" t="n">
+        <v>-43.9127375087966</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>-57.8014184397163</v>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>23.1818181818182</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="5" t="s">
+      <c r="A42" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B42" s="7"/>
-      <c r="C42" s="7" t="n">
-        <v>-43.9127375087966</v>
-      </c>
-      <c r="D42" s="7" t="n">
-        <v>-57.8014184397163</v>
-      </c>
-      <c r="E42" s="8" t="n">
-        <v>23.1818181818182</v>
+      <c r="B42" s="5"/>
+      <c r="C42" s="5" t="n">
+        <v>38.0175658720201</v>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>24.7899159663866</v>
+      </c>
+      <c r="E42" s="6" t="n">
+        <v>-23.4317343173432</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="5" t="s">
+      <c r="A43" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B43" s="7"/>
-      <c r="C43" s="7" t="n">
-        <v>38.0175658720201</v>
-      </c>
-      <c r="D43" s="7" t="n">
-        <v>24.7899159663866</v>
-      </c>
-      <c r="E43" s="8" t="n">
-        <v>-23.4317343173432</v>
-      </c>
+      <c r="B43" s="5"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="6"/>
     </row>
     <row r="44" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="5" t="s">
+      <c r="A44" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="8"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="6"/>
     </row>
     <row r="45" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="5" t="s">
+      <c r="A45" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B45" s="7"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="8"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="6"/>
     </row>
     <row r="46" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="5" t="s">
+      <c r="A46" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="8"/>
+      <c r="B46" s="5"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="6"/>
     </row>
     <row r="47" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="5" t="s">
+      <c r="A47" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B47" s="7"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="8"/>
+      <c r="B47" s="5" t="n">
+        <v>-47.1578947368421</v>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>17.5365344467641</v>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>23.9655172413793</v>
+      </c>
+      <c r="E47" s="6" t="n">
+        <v>8.32</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="5" t="s">
+      <c r="A48" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B48" s="7" t="n">
-        <v>-47.1578947368421</v>
-      </c>
-      <c r="C48" s="7" t="n">
-        <v>17.5365344467641</v>
-      </c>
-      <c r="D48" s="7" t="n">
-        <v>23.9655172413793</v>
-      </c>
-      <c r="E48" s="8" t="n">
-        <v>8.32</v>
+      <c r="B48" s="5" t="n">
+        <v>13.4351482957061</v>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>-12.9662522202487</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>-0.139082058414465</v>
+      </c>
+      <c r="E48" s="6" t="n">
+        <v>11.0782865583456</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="5" t="s">
+      <c r="A49" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B49" s="7" t="n">
-        <v>13.4351482957061</v>
-      </c>
-      <c r="C49" s="7" t="n">
-        <v>-12.9662522202487</v>
-      </c>
-      <c r="D49" s="7" t="n">
-        <v>-0.139082058414465</v>
-      </c>
-      <c r="E49" s="8" t="n">
-        <v>11.0782865583456</v>
-      </c>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
     </row>
     <row r="50" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="5" t="s">
+      <c r="A50" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B50" s="5"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="5"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
     </row>
     <row r="51" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="5" t="s">
+      <c r="A51" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B51" s="5"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="5"/>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
     </row>
     <row r="52" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="5" t="s">
+      <c r="A52" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B52" s="5"/>
-      <c r="C52" s="5"/>
-      <c r="D52" s="5"/>
+      <c r="B52" s="3"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
     </row>
     <row r="53" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="5" t="s">
+      <c r="A53" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B53" s="5"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="5"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
     </row>
     <row r="54" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="5" t="s">
+      <c r="A54" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B54" s="5"/>
-      <c r="C54" s="5"/>
-      <c r="D54" s="5"/>
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
     </row>
     <row r="55" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="5" t="s">
+      <c r="A55" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B55" s="5"/>
-      <c r="C55" s="5"/>
-      <c r="D55" s="5"/>
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
     </row>
     <row r="56" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="5" t="s">
+      <c r="A56" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B56" s="5"/>
-      <c r="C56" s="5"/>
-      <c r="D56" s="5"/>
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
     </row>
     <row r="57" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="5" t="s">
+      <c r="A57" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B57" s="5"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="5"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
     </row>
     <row r="58" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="5" t="s">
+      <c r="A58" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B58" s="5"/>
-      <c r="C58" s="5"/>
-      <c r="D58" s="5"/>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
     </row>
     <row r="59" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="5" t="s">
+      <c r="A59" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B59" s="5"/>
-      <c r="C59" s="5"/>
-      <c r="D59" s="5"/>
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
     </row>
     <row r="60" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="5" t="s">
+      <c r="A60" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B60" s="5"/>
-      <c r="C60" s="5"/>
-      <c r="D60" s="5"/>
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
     </row>
     <row r="61" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="5" t="s">
+      <c r="A61" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B61" s="5"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="5"/>
+      <c r="B61" s="3"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3"/>
     </row>
     <row r="62" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="5" t="s">
+      <c r="A62" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B62" s="5"/>
-      <c r="C62" s="5"/>
-      <c r="D62" s="5"/>
+      <c r="B62" s="3"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
     </row>
     <row r="63" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="5" t="s">
+      <c r="A63" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B63" s="5"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="5"/>
+      <c r="B63" s="3"/>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
     </row>
     <row r="64" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="5" t="s">
+      <c r="A64" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B64" s="5"/>
-      <c r="C64" s="5"/>
-      <c r="D64" s="5"/>
+      <c r="B64" s="3"/>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
     </row>
     <row r="65" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="5" t="s">
+      <c r="A65" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B65" s="5"/>
-      <c r="C65" s="5"/>
-      <c r="D65" s="5"/>
+      <c r="B65" s="3"/>
+      <c r="C65" s="3"/>
+      <c r="D65" s="3"/>
     </row>
     <row r="66" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="5" t="s">
+      <c r="A66" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B66" s="5"/>
-      <c r="C66" s="5"/>
-      <c r="D66" s="5"/>
+      <c r="B66" s="3"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="3"/>
     </row>
     <row r="67" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="5" t="s">
+      <c r="A67" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B67" s="5"/>
-      <c r="C67" s="5"/>
-      <c r="D67" s="5"/>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
     </row>
     <row r="68" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="5" t="s">
+      <c r="A68" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B68" s="5"/>
-      <c r="C68" s="5"/>
-      <c r="D68" s="5"/>
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3"/>
     </row>
     <row r="69" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="5" t="s">
+      <c r="A69" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B69" s="5"/>
-      <c r="C69" s="5"/>
-      <c r="D69" s="5"/>
+      <c r="B69" s="3"/>
+      <c r="C69" s="3"/>
+      <c r="D69" s="3"/>
     </row>
     <row r="70" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="5" t="s">
+      <c r="A70" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B70" s="5"/>
-      <c r="C70" s="5"/>
-      <c r="D70" s="5"/>
+      <c r="B70" s="3"/>
+      <c r="C70" s="3"/>
+      <c r="D70" s="3"/>
     </row>
     <row r="71" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="5" t="s">
+      <c r="A71" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B71" s="5"/>
-      <c r="C71" s="5"/>
-      <c r="D71" s="5"/>
+      <c r="B71" s="3"/>
+      <c r="C71" s="3"/>
+      <c r="D71" s="3"/>
     </row>
     <row r="72" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="5" t="s">
+      <c r="A72" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B72" s="3"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3"/>
+    </row>
+    <row r="73" customFormat="false" ht="40.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B72" s="5"/>
-      <c r="C72" s="5"/>
-      <c r="D72" s="5"/>
-    </row>
-    <row r="73" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B73" s="5"/>
-      <c r="C73" s="5"/>
-      <c r="D73" s="5"/>
-    </row>
-    <row r="74" customFormat="false" ht="40.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="9" t="s">
+      <c r="B73" s="7"/>
+      <c r="C73" s="7"/>
+      <c r="D73" s="7"/>
+    </row>
+    <row r="74" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="B74" s="9"/>
-      <c r="C74" s="9"/>
-      <c r="D74" s="9"/>
-    </row>
-    <row r="75" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="10" t="s">
+      <c r="B74" s="8"/>
+      <c r="C74" s="8"/>
+      <c r="D74" s="8"/>
+    </row>
+    <row r="75" s="9" customFormat="true" ht="17.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="B75" s="10"/>
-      <c r="C75" s="10"/>
-      <c r="D75" s="10"/>
-    </row>
-    <row r="76" s="11" customFormat="true" ht="17.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="11" t="s">
+    </row>
+    <row r="76" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="77" s="11" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="11" t="s">
+    <row r="77" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="9" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="78" s="11" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="11" t="s">
+    <row r="78" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="9" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="79" s="11" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="11" t="s">
+    <row r="79" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="9" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="80" s="11" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="11" t="s">
+    <row r="80" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="9" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="81" s="11" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="11" t="s">
+    <row r="81" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="9" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="82" s="11" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="11" t="s">
+    <row r="82" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="9" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="83" s="11" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="11" t="s">
+    <row r="83" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="9" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="84" s="11" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="11" t="s">
+    <row r="84" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="9" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="85" s="11" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="11" t="s">
+    <row r="85" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="1" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="3" t="s">
+      <c r="A86" s="0" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="0" t="s">
-        <v>89</v>
-      </c>
-    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="2">
+    <mergeCell ref="A73:D73"/>
     <mergeCell ref="A74:D74"/>
-    <mergeCell ref="A75:D75"/>
-    <mergeCell ref="76:76"/>
-    <mergeCell ref="77:77"/>
-    <mergeCell ref="78:78"/>
-    <mergeCell ref="79:79"/>
-    <mergeCell ref="80:80"/>
-    <mergeCell ref="81:81"/>
-    <mergeCell ref="82:82"/>
-    <mergeCell ref="83:83"/>
-    <mergeCell ref="84:84"/>
-    <mergeCell ref="85:85"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>

--- a/agriculture 44.xlsx
+++ b/agriculture 44.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="88">
   <si>
     <t xml:space="preserve">Year</t>
   </si>
@@ -245,6 +245,9 @@
   </si>
   <si>
     <t xml:space="preserve">2019-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unit:- </t>
   </si>
   <si>
     <r>
@@ -254,7 +257,6 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Source:</t>
     </r>
@@ -264,22 +266,36 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> EPWRF( Economic and Political Weekly Research Foundation) 1950-2020</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Footnote Description:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">: Telangana:-&gt; On 2 June 2014, Telangana was separated from Andhra Pradesh as the 29th state of India. However Indian Horticulture Database disseminated separate data for both Andhra Pradesh &amp; Telangana in the year 2013-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">:-&gt; Data for Daman and Diu are included under Goa, Daman and Diu for the years 1962-63 To 1979-80.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">:-&gt; Data for Haryana are included under Punjab for the years 1962-63 To 1964-65.</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Footnote Description: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Telangana:-&gt; On 2 June 2014, Telangana was separated from Andhra Pradesh as the 29th state of India. However Indian Horticulture Database disseminated separate data for both Andhra Pradesh &amp; Telangana in the year 2013-14</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Data for Daman and Diu are included under Goa, Daman and Diu for the years 1962-63 To 1979-80.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data for Haryana are included under Punjab for the years 1962-63 To 1964-65.</t>
   </si>
   <si>
     <t xml:space="preserve">1962-63 to 2013-14 - Plantation Crops: Coffee: Area:-&gt; Area refers to the total planted area.</t>
@@ -303,10 +319,25 @@
     <t xml:space="preserve">Plantation Crops: Coffee: Yield:-&gt; Coffee Yield is based on plucked area.</t>
   </si>
   <si>
-    <t xml:space="preserve">Discription</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Directorate of Economics and Statistics, Dept. of Agriculture, Cooperation and Farmers Welfare, Ministry of Agriculture, Govt. of India</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Discription:- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Directorate of Economics and Statistics, Dept. of Agriculture, Cooperation and Farmers Welfare, Ministry of Agriculture, Govt. of India</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -317,7 +348,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -347,6 +378,19 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -412,7 +456,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -441,15 +485,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -470,7 +522,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E1048576"/>
+  <dimension ref="A1:E86"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="11.44"/>
@@ -1213,87 +1265,141 @@
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
     </row>
-    <row r="73" customFormat="false" ht="40.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="7" t="s">
+    <row r="73" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B73" s="7"/>
-      <c r="C73" s="7"/>
-      <c r="D73" s="7"/>
-    </row>
-    <row r="74" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="8" t="s">
+      <c r="B73" s="3"/>
+      <c r="C73" s="3"/>
+      <c r="D73" s="3"/>
+      <c r="E73" s="3"/>
+    </row>
+    <row r="74" customFormat="false" ht="40.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B74" s="8"/>
-      <c r="C74" s="8"/>
-      <c r="D74" s="8"/>
-    </row>
-    <row r="75" s="9" customFormat="true" ht="17.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="9" t="s">
+      <c r="B74" s="7"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="7"/>
+      <c r="E74" s="7"/>
+    </row>
+    <row r="75" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="8" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="76" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B75" s="8"/>
+      <c r="C75" s="8"/>
+      <c r="D75" s="8"/>
+      <c r="E75" s="8"/>
+    </row>
+    <row r="76" s="10" customFormat="true" ht="17.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="9" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="77" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B76" s="9"/>
+      <c r="C76" s="9"/>
+      <c r="D76" s="9"/>
+      <c r="E76" s="9"/>
+    </row>
+    <row r="77" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="9" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="78" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B77" s="9"/>
+      <c r="C77" s="9"/>
+      <c r="D77" s="9"/>
+      <c r="E77" s="9"/>
+    </row>
+    <row r="78" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="9" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="79" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B78" s="9"/>
+      <c r="C78" s="9"/>
+      <c r="D78" s="9"/>
+      <c r="E78" s="9"/>
+    </row>
+    <row r="79" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="9" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="80" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B79" s="9"/>
+      <c r="C79" s="9"/>
+      <c r="D79" s="9"/>
+      <c r="E79" s="9"/>
+    </row>
+    <row r="80" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="9" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="81" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B80" s="9"/>
+      <c r="C80" s="9"/>
+      <c r="D80" s="9"/>
+      <c r="E80" s="9"/>
+    </row>
+    <row r="81" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="9" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="82" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B81" s="9"/>
+      <c r="C81" s="9"/>
+      <c r="D81" s="9"/>
+      <c r="E81" s="9"/>
+    </row>
+    <row r="82" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="9" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="83" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B82" s="9"/>
+      <c r="C82" s="9"/>
+      <c r="D82" s="9"/>
+      <c r="E82" s="9"/>
+    </row>
+    <row r="83" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="9" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="84" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B83" s="9"/>
+      <c r="C83" s="9"/>
+      <c r="D83" s="9"/>
+      <c r="E83" s="9"/>
+    </row>
+    <row r="84" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="9" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="85" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="1" t="s">
+      <c r="B84" s="9"/>
+      <c r="C84" s="9"/>
+      <c r="D84" s="9"/>
+      <c r="E84" s="9"/>
+    </row>
+    <row r="85" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="11" t="s">
         <v>87</v>
       </c>
+      <c r="B85" s="11"/>
+      <c r="C85" s="11"/>
+      <c r="D85" s="11"/>
+      <c r="E85" s="11"/>
     </row>
     <row r="86" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="0" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="A86" s="1"/>
+    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A73:D73"/>
-    <mergeCell ref="A74:D74"/>
+  <mergeCells count="13">
+    <mergeCell ref="A73:E73"/>
+    <mergeCell ref="A74:E74"/>
+    <mergeCell ref="A75:E75"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A80:E80"/>
+    <mergeCell ref="A81:E81"/>
+    <mergeCell ref="A82:E82"/>
+    <mergeCell ref="A83:E83"/>
+    <mergeCell ref="A84:E84"/>
+    <mergeCell ref="A85:E85"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>

--- a/agriculture 44.xlsx
+++ b/agriculture 44.xlsx
@@ -247,7 +247,7 @@
     <t xml:space="preserve">2019-20</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit:- </t>
+    <t xml:space="preserve">Unit:- Percentage(%)</t>
   </si>
   <si>
     <r>
@@ -257,6 +257,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Source:</t>
     </r>
@@ -266,6 +267,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> EPWRF( Economic and Political Weekly Research Foundation) 1950-2020</t>
     </r>
@@ -278,6 +280,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Footnote Description: </t>
     </r>
@@ -287,6 +290,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Telangana:-&gt; On 2 June 2014, Telangana was separated from Andhra Pradesh as the 29th state of India. However Indian Horticulture Database disseminated separate data for both Andhra Pradesh &amp; Telangana in the year 2013-14</t>
     </r>
@@ -326,6 +330,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Discription:- </t>
     </r>
@@ -335,6 +340,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Directorate of Economics and Statistics, Dept. of Agriculture, Cooperation and Farmers Welfare, Ministry of Agriculture, Govt. of India</t>
     </r>
@@ -348,7 +354,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -378,19 +384,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -456,7 +449,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -485,23 +478,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1292,95 +1281,59 @@
       <c r="D75" s="8"/>
       <c r="E75" s="8"/>
     </row>
-    <row r="76" s="10" customFormat="true" ht="17.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="76" s="9" customFormat="true" ht="17.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="B76" s="9"/>
-      <c r="C76" s="9"/>
-      <c r="D76" s="9"/>
-      <c r="E76" s="9"/>
-    </row>
-    <row r="77" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="77" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="B77" s="9"/>
-      <c r="C77" s="9"/>
-      <c r="D77" s="9"/>
-      <c r="E77" s="9"/>
-    </row>
-    <row r="78" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="78" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="B78" s="9"/>
-      <c r="C78" s="9"/>
-      <c r="D78" s="9"/>
-      <c r="E78" s="9"/>
-    </row>
-    <row r="79" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="79" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="B79" s="9"/>
-      <c r="C79" s="9"/>
-      <c r="D79" s="9"/>
-      <c r="E79" s="9"/>
-    </row>
-    <row r="80" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="80" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="B80" s="9"/>
-      <c r="C80" s="9"/>
-      <c r="D80" s="9"/>
-      <c r="E80" s="9"/>
-    </row>
-    <row r="81" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="81" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="B81" s="9"/>
-      <c r="C81" s="9"/>
-      <c r="D81" s="9"/>
-      <c r="E81" s="9"/>
-    </row>
-    <row r="82" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="82" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="B82" s="9"/>
-      <c r="C82" s="9"/>
-      <c r="D82" s="9"/>
-      <c r="E82" s="9"/>
-    </row>
-    <row r="83" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="83" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="B83" s="9"/>
-      <c r="C83" s="9"/>
-      <c r="D83" s="9"/>
-      <c r="E83" s="9"/>
-    </row>
-    <row r="84" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="84" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="B84" s="9"/>
-      <c r="C84" s="9"/>
-      <c r="D84" s="9"/>
-      <c r="E84" s="9"/>
-    </row>
-    <row r="85" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="11" t="s">
+    </row>
+    <row r="85" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="B85" s="11"/>
-      <c r="C85" s="11"/>
-      <c r="D85" s="11"/>
-      <c r="E85" s="11"/>
+      <c r="B85" s="10"/>
+      <c r="C85" s="10"/>
+      <c r="D85" s="10"/>
+      <c r="E85" s="10"/>
     </row>
     <row r="86" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1"/>

--- a/agriculture 44.xlsx
+++ b/agriculture 44.xlsx
@@ -247,7 +247,7 @@
     <t xml:space="preserve">2019-20</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit:- Percentage(%)</t>
+    <t xml:space="preserve">Unit:- Percentage (%)</t>
   </si>
   <si>
     <r>
